--- a/final_data_pipeline/output/322291_elec_options.xlsx
+++ b/final_data_pipeline/output/322291_elec_options.xlsx
@@ -1365,7 +1365,7 @@
         <v>68</v>
       </c>
       <c r="AD8">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE8">
         <v>8000</v>
@@ -1463,7 +1463,7 @@
         <v>68</v>
       </c>
       <c r="AD9">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE9">
         <v>8000</v>
@@ -1561,7 +1561,7 @@
         <v>68</v>
       </c>
       <c r="AD10">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE10">
         <v>8000</v>
@@ -1659,7 +1659,7 @@
         <v>68</v>
       </c>
       <c r="AD11">
-        <v>10</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="AE11">
         <v>8000</v>
@@ -1754,7 +1754,7 @@
         <v>68</v>
       </c>
       <c r="AD12">
-        <v>10</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="AE12">
         <v>8000</v>
@@ -1852,7 +1852,7 @@
         <v>68</v>
       </c>
       <c r="AD13">
-        <v>10</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="AE13">
         <v>8000</v>
@@ -3987,7 +3987,7 @@
         <v>68</v>
       </c>
       <c r="AD35">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE35">
         <v>8000</v>
@@ -4085,7 +4085,7 @@
         <v>68</v>
       </c>
       <c r="AD36">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE36">
         <v>8000</v>
@@ -4180,7 +4180,7 @@
         <v>68</v>
       </c>
       <c r="AD37">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE37">
         <v>8000</v>
@@ -4278,7 +4278,7 @@
         <v>68</v>
       </c>
       <c r="AD38">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE38">
         <v>8000</v>
@@ -4373,7 +4373,7 @@
         <v>68</v>
       </c>
       <c r="AD39">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE39">
         <v>8000</v>
@@ -4471,7 +4471,7 @@
         <v>68</v>
       </c>
       <c r="AD40">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE40">
         <v>8000</v>
